--- a/syllabus/2025-2-Planning.xlsx
+++ b/syllabus/2025-2-Planning.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ea47/Documents/GitPages/socialcomputing/syllabus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ea47/Documents/CalvinU/TeachingPages/25fa-social-modeling/syllabus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D729232-1893-5E48-9EBA-A7D4175E60A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140059E0-AA08-C849-9B98-E7CA77A57821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-68800" yWindow="500" windowWidth="34400" windowHeight="28300" xr2:uid="{70130527-71ED-5B42-96F8-E7F1D0F06094}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34400" windowHeight="21580" xr2:uid="{70130527-71ED-5B42-96F8-E7F1D0F06094}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Week</t>
   </si>
@@ -78,13 +78,25 @@
   </si>
   <si>
     <t>SIR Model</t>
+  </si>
+  <si>
+    <t>Final Project - Phase 1</t>
+  </si>
+  <si>
+    <t>Final Project - Phase 2</t>
+  </si>
+  <si>
+    <t>Final Project - Phase 3</t>
+  </si>
+  <si>
+    <t>Final Project - Presentations</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -95,6 +107,13 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -241,7 +260,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -260,13 +279,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -280,13 +292,32 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -467,6 +498,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -474,15 +514,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -502,7 +533,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{871E6D65-07A5-0249-9427-6196F1949075}" name="Table1" displayName="Table1" ref="A1:G17" totalsRowShown="0" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{871E6D65-07A5-0249-9427-6196F1949075}" name="Table1" displayName="Table1" ref="A1:G17" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G17" xr:uid="{871E6D65-07A5-0249-9427-6196F1949075}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1515253A-E572-A84C-8E50-224DD7064F66}" name="Week" dataDxfId="6"/>
@@ -841,8 +872,8 @@
   <cols>
     <col min="1" max="2" width="10.83203125" style="1"/>
     <col min="3" max="3" width="47.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="18" customWidth="1"/>
-    <col min="5" max="5" width="11" style="18" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="13" customWidth="1"/>
+    <col min="5" max="5" width="11" style="13" customWidth="1"/>
     <col min="6" max="6" width="21.1640625" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
   </cols>
@@ -857,16 +888,16 @@
       <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -880,10 +911,10 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="15">
+      <c r="D2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="12">
         <f>1-D2</f>
         <v>0.5</v>
       </c>
@@ -900,10 +931,10 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="15">
+      <c r="D3" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="12">
         <f t="shared" ref="E3:E17" si="0">1-D3</f>
         <v>0.5</v>
       </c>
@@ -920,10 +951,10 @@
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>0.75</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="12">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
@@ -942,10 +973,10 @@
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="11">
         <v>0.75</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="12">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
@@ -964,10 +995,10 @@
       <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="11">
         <v>0.75</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="12">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
@@ -986,10 +1017,10 @@
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="D7" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
@@ -1008,10 +1039,10 @@
       <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="D8" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="12">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
@@ -1028,10 +1059,10 @@
       <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="11">
         <v>0.25</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -1048,10 +1079,10 @@
       <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <v>0.25</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -1068,10 +1099,10 @@
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <v>0.25</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -1079,112 +1110,124 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12" s="14">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="15">
         <v>45972</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="15">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="C12" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="18">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="A13" s="14">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="15">
         <v>45979</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="15">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="C13" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="18">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="15">
         <v>45986</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="C14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="18">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="A15" s="14">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="15">
         <v>45993</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="15">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="C15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="18">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="A16" s="14">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="15">
         <v>46000</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="15">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="C16" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="18">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
+      <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="20">
         <v>46007</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="17">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="C17" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="22">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
